--- a/docs/Mapping_casi_uso/matrimoni/Sep_Div_007.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Sep_Div_007.xlsx
@@ -50,10 +50,10 @@
     <t>Sentenza straniera</t>
   </si>
   <si>
+    <t>Dichiarazione di conformità</t>
+  </si>
+  <si>
     <t>NO</t>
-  </si>
-  <si>
-    <t>Dichiarazione di conformità</t>
   </si>
   <si>
     <t>Certificato di cui all’art.39 del Regolamento (CE) n. 2201/2003</t>
@@ -658,7 +658,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -678,10 +678,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -704,7 +704,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -727,7 +727,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -750,7 +750,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -773,7 +773,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -957,7 +957,7 @@
         <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>33</v>
@@ -1118,7 +1118,7 @@
         <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>43</v>
@@ -1141,7 +1141,7 @@
         <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>43</v>
@@ -1164,7 +1164,7 @@
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>43</v>
@@ -1187,7 +1187,7 @@
         <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>43</v>
@@ -1210,7 +1210,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>43</v>
@@ -1233,7 +1233,7 @@
         <v>64</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>43</v>
@@ -1279,7 +1279,7 @@
         <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>33</v>
@@ -1302,7 +1302,7 @@
         <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>72</v>
@@ -1371,7 +1371,7 @@
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>72</v>
@@ -1394,7 +1394,7 @@
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>72</v>
@@ -1417,7 +1417,7 @@
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>72</v>
@@ -1486,7 +1486,7 @@
         <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>72</v>
@@ -1509,7 +1509,7 @@
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>72</v>
@@ -1532,7 +1532,7 @@
         <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>72</v>
@@ -1555,7 +1555,7 @@
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>72</v>
@@ -1578,7 +1578,7 @@
         <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>72</v>
@@ -1647,7 +1647,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>72</v>
@@ -1670,7 +1670,7 @@
         <v>104</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>72</v>
@@ -1693,7 +1693,7 @@
         <v>106</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>72</v>
@@ -1716,7 +1716,7 @@
         <v>108</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>72</v>
@@ -1739,7 +1739,7 @@
         <v>110</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>72</v>
@@ -1762,7 +1762,7 @@
         <v>112</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>72</v>
@@ -1785,7 +1785,7 @@
         <v>114</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>72</v>
@@ -1808,7 +1808,7 @@
         <v>116</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>72</v>
@@ -1831,7 +1831,7 @@
         <v>118</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>72</v>
@@ -1992,7 +1992,7 @@
         <v>53</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>127</v>
@@ -2015,7 +2015,7 @@
         <v>55</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>127</v>
@@ -2038,7 +2038,7 @@
         <v>58</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>127</v>
@@ -2061,7 +2061,7 @@
         <v>60</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>127</v>
@@ -2084,7 +2084,7 @@
         <v>129</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>127</v>
@@ -2107,7 +2107,7 @@
         <v>131</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>127</v>
@@ -2130,7 +2130,7 @@
         <v>134</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>135</v>
@@ -2314,7 +2314,7 @@
         <v>150</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>135</v>
@@ -2337,7 +2337,7 @@
         <v>151</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>135</v>
@@ -2360,7 +2360,7 @@
         <v>153</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>135</v>
@@ -2383,7 +2383,7 @@
         <v>155</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>135</v>
@@ -2429,7 +2429,7 @@
         <v>75</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>160</v>
@@ -2475,7 +2475,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>160</v>
@@ -2590,7 +2590,7 @@
         <v>89</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>160</v>
@@ -2613,7 +2613,7 @@
         <v>91</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>160</v>
@@ -2636,7 +2636,7 @@
         <v>93</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>160</v>
@@ -2659,7 +2659,7 @@
         <v>95</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>160</v>
@@ -2682,7 +2682,7 @@
         <v>62</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>160</v>
@@ -2751,7 +2751,7 @@
         <v>102</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>160</v>
@@ -2774,7 +2774,7 @@
         <v>104</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>160</v>
@@ -2797,7 +2797,7 @@
         <v>106</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>160</v>
@@ -2820,7 +2820,7 @@
         <v>108</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>160</v>
@@ -2843,7 +2843,7 @@
         <v>110</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>160</v>
@@ -2866,7 +2866,7 @@
         <v>112</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>160</v>
@@ -2889,7 +2889,7 @@
         <v>114</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>160</v>
@@ -2912,7 +2912,7 @@
         <v>116</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>160</v>
@@ -2935,7 +2935,7 @@
         <v>118</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>160</v>
@@ -3027,7 +3027,7 @@
         <v>161</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>160</v>
@@ -3050,7 +3050,7 @@
         <v>163</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>160</v>
@@ -3073,7 +3073,7 @@
         <v>165</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>160</v>
@@ -3096,7 +3096,7 @@
         <v>167</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>160</v>
@@ -3119,7 +3119,7 @@
         <v>75</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>170</v>
@@ -3165,7 +3165,7 @@
         <v>79</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>170</v>
@@ -3280,7 +3280,7 @@
         <v>89</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>170</v>
@@ -3303,7 +3303,7 @@
         <v>91</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>170</v>
@@ -3326,7 +3326,7 @@
         <v>93</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>170</v>
@@ -3349,7 +3349,7 @@
         <v>95</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>170</v>
@@ -3372,7 +3372,7 @@
         <v>62</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>170</v>
@@ -3441,7 +3441,7 @@
         <v>102</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>170</v>
@@ -3464,7 +3464,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>170</v>
@@ -3487,7 +3487,7 @@
         <v>106</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>170</v>
@@ -3510,7 +3510,7 @@
         <v>108</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>170</v>
@@ -3533,7 +3533,7 @@
         <v>110</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>170</v>
@@ -3556,7 +3556,7 @@
         <v>112</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>170</v>
@@ -3579,7 +3579,7 @@
         <v>114</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>170</v>
@@ -3602,7 +3602,7 @@
         <v>116</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>170</v>
@@ -3625,7 +3625,7 @@
         <v>118</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>170</v>
@@ -3717,7 +3717,7 @@
         <v>161</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>170</v>
@@ -3740,7 +3740,7 @@
         <v>163</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>170</v>
@@ -3763,7 +3763,7 @@
         <v>165</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>170</v>
@@ -3786,7 +3786,7 @@
         <v>167</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>170</v>
